--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_788_Tunisia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_788_Tunisia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R53504951b8954b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8f5db89de5b7486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R06a008a95abc4daf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R561d320ab1ff4584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R578d9ff7643e4fb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R40b5c995f4e04e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf7c630e44d5c447d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R54ecb7b934a64183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Red5d3c712faf40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R23a5721c8d23457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4c307be7a1d540cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R927e55ea72e24181"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ788CommercialTable" displayName="EEZ788CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ788CommercialTable" displayName="EEZ788CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ788FunctionalTable" displayName="EEZ788FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ788FunctionalTable" displayName="EEZ788FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ788ValidationTable" displayName="EEZ788ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ788ValidationTable" displayName="EEZ788ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11883,7 +11837,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096447b5f81a47b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798f9fa8e6904617"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11893,20 +11847,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11914,660 +11858,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5401.3294704729</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.110194110306132</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.88254706076276</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5401.3294704729</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.88893471144837</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$168,A2,'Species'!$U$2:$U$168))</x:f>
-        <x:v>696171.6014748036</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.110194110306132</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.88254706076276</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>696137.0996689083</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>34.50180589535739</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000495617973986</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000049561797398482126</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.560902109</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9473640332614526</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>885.8578403105187</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.560902109</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>978.2433354488421</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$168,A3,'Species'!$U$2:$U$168))</x:f>
-        <x:v>2505.1854208661343</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9473640332614526</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>885.8578403105187</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2268.5952115253926</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>236.5902093407417</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1042893012110608</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10428930121106073</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6834.280748118899</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.117914200583735</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>131.1940685813618</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6834.280748118899</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>157.65047467953326</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$168,A4,'Species'!$U$2:$U$168))</x:f>
-        <x:v>1077427.6040341402</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.117914200583735</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>131.1940685813618</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>896617.0971729915</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>180810.50686114875</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2016585535020905</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.20165855350209047</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>875.8002111566</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.207629846048284</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>161.29832075127496</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>875.8002111566</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>161.47438439643224</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$168,A5,'Species'!$U$2:$U$168))</x:f>
-        <x:v>141419.29995077735</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.207629846048284</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>161.29832075127496</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>141265.1033731716</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>154.1965776057623</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0010915404719483</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0010915404719481952</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>14216.684024558099</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.7701233138865913</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>58.90108757845266</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>14216.684024558099</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>58.91113006833639</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$168,A6,'Species'!$U$2:$U$168))</x:f>
-        <x:v>837520.9217111822</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.7701233138865913</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>58.90108757845266</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>837378.1508056854</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>142.77090549678542</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0001704975289354</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00017049752893530604</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1108.6388818169003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0592959005117204</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.462936867186876</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1108.6388818169003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>13.396362505942356</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$168,A7,'Species'!$U$2:$U$168))</x:f>
-        <x:v>14851.728349001782</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0592959005117204</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.462936867186876</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>12708.25751077578</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2143.4708382260014</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1686675640943283</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16866756409432818</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>53691.3501630257</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4184274702423743</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>262.0761319381131</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>53691.3501630257</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>431.8045386202081</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$168,A8,'Species'!$U$2:$U$168))</x:f>
-        <x:v>23184168.68504135</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4184274702423743</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>262.0761319381131</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>14071221.369260555</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>9112947.315780794</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.647630157797715</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6476301577977152</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>39544.8543579449</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4250047350161634</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>266.07540692506205</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>39544.8543579449</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>583.4458816823972</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$168,A9,'Species'!$U$2:$U$168))</x:f>
-        <x:v>23072282.41687315</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4250047350161634</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>266.07540692506205</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10521913.215082504</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>12550369.201790646</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.19278394957682</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.19278394957682</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1200.3432482959</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7665156837839047</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>584.1383018427168</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1200.3432482959</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>597.6775690009301</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$168,A10,'Species'!$U$2:$U$168))</x:f>
-        <x:v>717418.2346081734</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7665156837839047</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>584.1383018427168</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>701166.4666879376</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>16251.767920235754</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0231781876235515</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.02317818762355159</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3228.0118937155</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9043317411688543</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>802.29066895645</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3228.0118937155</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>945.8718218832564</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$168,A11,'Species'!$U$2:$U$168))</x:f>
-        <x:v>3053285.4909695005</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9043317411688543</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>802.29066895645</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2589803.821608385</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>463481.66936111543</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1789640070394491</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.17896400703944917</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7184.712369936799</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.480216531579378</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3021.4577905577403</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7184.712369936799</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3039.3496255957084</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$168,A12,'Species'!$U$2:$U$168))</x:f>
-        <x:v>21836852.851580266</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.480216531579378</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3021.4577905577403</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>21708305.163062107</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>128547.68851815909</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.005921590264766</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.005921590264766048</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6431060ba18e45d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79111ab48dd54812"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12577,20 +12092,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12598,1416 +12103,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10632.850381054399</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.0319754301607</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1076.404315252641</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10632.850381054399</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1333.3822616117393</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$168,A2,'Species'!$U$2:$U$168))</x:f>
-        <x:v>14177654.088469557</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.0319754301607</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1076.404315252641</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11445246.033602644</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2732408.0548669137</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2387373802926305</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.23873738029263036</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>71.855575089</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.847284358382654</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>703.5328138150583</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>71.855575089</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>750.2604597199216</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$168,A3,'Species'!$U$2:$U$168))</x:f>
-        <x:v>53910.396799712486</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.847284358382654</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>703.5328138150583</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>50552.754930663374</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3357.641869049112</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0664185735011742</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06641857350117421</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>400.41685835190003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.356622329423272</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>227.31198236450106</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>400.41685835190003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1731.0349234168173</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$168,A4,'Species'!$U$2:$U$168))</x:f>
-        <x:v>693135.5657319839</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.356622329423272</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>227.31198236450106</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>91019.54984413603</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>602116.0158878479</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>7.615238340762234</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>6.615238340762234</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>218.6536087433</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6060528797443845</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>403.6945438677631</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>218.6536087433</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>466.7036546845833</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$168,A5,'Species'!$U$2:$U$168))</x:f>
-        <x:v>102046.43831047106</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6060528797443845</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>403.6945438677631</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>88269.26884666683</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>13777.169463804225</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.156081155353588</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.1560811553535879</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.060862065</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.060862065</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$168,A6,'Species'!$U$2:$U$168))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>139.42693598914974</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>139.42693598914974</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6132.3718203749995</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.456781326209469</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2862.7361763193626</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6132.3718203749995</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2886.1476837134715</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$168,A7,'Species'!$U$2:$U$168))</x:f>
-        <x:v>17698930.72504507</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.456781326209469</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2862.7361763193626</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>17555362.656828936</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>143568.06821613386</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0081780177956214</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.008178017795621368</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1259.4897883698</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6113606005288204</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>408.6585601823475</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1259.4897883698</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>409.38181982666964</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$168,A8,'Species'!$U$2:$U$168))</x:f>
-        <x:v>515612.22161593573</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6113606005288204</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>408.6585601823475</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>514701.28347957204</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>910.938136363693</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0017698384783604</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0017698384783605213</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>282.23941117040005</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.250887573984198</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1781.9174219392557</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>282.23941117040005</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2161.6007914752286</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$168,A9,'Species'!$U$2:$U$168))</x:f>
-        <x:v>610088.9345714392</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.250887573984198</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1781.9174219392557</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>502927.3239224128</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>107161.61064902635</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2130757378884396</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2130757378884395</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>579.3652494716998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.906332394836221</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>805.9950875488953</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>579.3652494716998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>838.1976002926853</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$168,A10,'Species'!$U$2:$U$168))</x:f>
-        <x:v>485622.5618001517</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.906332394836221</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>805.9950875488953</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>466965.54497073026</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>18657.016829421453</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0399537332686737</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03995373326867379</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>300.9808728611</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3206551613306137</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>209.2450347844878</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>300.9808728611</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>224.2291328636959</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$168,A11,'Species'!$U$2:$U$168))</x:f>
-        <x:v>67488.68013020276</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3206551613306137</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>209.2450347844878</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>62978.75321128638</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4509.926918916382</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0716102921851454</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.07161029218514542</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>176.68324305919998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.4600239329877285</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2884.1904399663504</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>176.68324305919998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2884.1960535296357</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$168,A12,'Species'!$U$2:$U$168))</x:f>
-        <x:v>509589.112356162</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.4600239329877285</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2884.1904399663504</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>509588.1205335956</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0.9918225663714111</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000001946321993</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0000019463219930104773</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.177257633</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.177257633</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$168,A13,'Species'!$U$2:$U$168))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>213.11054792036592</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>213.11054792036592</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>12446.803338734902</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.1180433483369763</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>131.23308804722038</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>12446.803338734902</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>240.90326165532184</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$168,A14,'Species'!$U$2:$U$168))</x:f>
-        <x:v>2998475.5214835876</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.1180433483369763</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>131.23308804722038</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1633432.438458634</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1365043.0830249535</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.83568995624518</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.8356899562451799</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>46287.3295861147</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2774257994828373</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>189.41998569713738</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>46287.3295861147</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>206.73145164686073</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$168,A15,'Species'!$U$2:$U$168))</x:f>
-        <x:v>9569046.838194177</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2774257994828373</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>189.41998569713738</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8767745.30816053</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>801301.5300336462</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0913919715810905</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.09139197158109043</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>20396.136837613503</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.707195511242291</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>509.56021389565524</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>20396.136837613503</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>997.7274547418446</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$168,A16,'Species'!$U$2:$U$168))</x:f>
-        <x:v>20349785.693558495</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.707195511242291</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>509.56021389565524</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>10393059.84961939</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>9956725.843939105</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.9580167908206296</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.9580167908206297</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3744.4556147444005</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2434178173859127</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>175.15309563310544</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3744.4556147444005</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>475.7103989461333</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$168,A17,'Species'!$U$2:$U$168))</x:f>
-        <x:v>1781276.4743261475</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2434178173859127</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>175.15309563310544</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>655852.9923832446</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1125423.4819429028</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.7159691196243974</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.7159691196243974</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1158.7367286497001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0567583639803138</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>11.39615543295224</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1158.7367286497001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>13.250407796047206</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$168,A18,'Species'!$U$2:$U$168))</x:f>
-        <x:v>15353.734182866223</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0567583639803138</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>11.39615543295224</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>13205.143865562584</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2148.5903173036386</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1627085883484316</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.16270858834843155</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>6533.2998752578</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.1085741806098492</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>128.4027072768657</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>6533.2998752578</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>154.5832799943361</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$168,A19,'Species'!$U$2:$U$168))</x:f>
-        <x:v>1009938.9239039375</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.1085741806098492</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>128.4027072768657</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>838893.3914347105</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>171045.53246922698</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2038942423621883</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.20389424236218834</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>94.7047004077</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>94.7047004077</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$168,A20,'Species'!$U$2:$U$168))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>22718.075292386926</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>22718.075292386926</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>534.0919482080999</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.5867403216398044</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>386.1360251133569</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>534.0919482080999</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>414.3459802892017</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$168,A21,'Species'!$U$2:$U$168))</x:f>
-        <x:v>221298.85184485468</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.5867403216398044</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>386.1360251133569</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>206232.14192612458</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>15066.709918730106</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0730570403721416</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.07305704037214154</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>19772.870217050004</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>2.8663867136023624</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>73.51682006818164</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>19772.870217050004</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>78.8067509943906</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$168,A22,'Species'!$U$2:$U$168))</x:f>
-        <x:v>1558235.6596394617</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>2.8663867136023624</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>73.51682006818164</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1453638.541978373</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>104597.1176610887</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.071955382745104</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.07195538274510396</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.096291161</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.096291161</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$168,A23,'Species'!$U$2:$U$168))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>12.404704499026137</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>12.404704499026137</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>875.7393490915999</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.2075497587171777</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>161.26857880992827</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>875.7393490915999</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>161.3263959891001</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$168,A24,'Species'!$U$2:$U$168))</x:f>
-        <x:v>141279.8730147882</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.2075497587171777</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>161.26857880992827</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>141229.24023593398</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>50.63277885422576</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0003585148427454</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.000358514842745312</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>0.594234018</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.572276404647033</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>373.4877866853382</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>0.594234018</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>400.3631707318744</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$168,A25,'Species'!$U$2:$U$168))</x:f>
-        <x:v>237.9094156032217</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.572276404647033</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>373.4877866853382</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>221.93914815595542</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>15.97026744726628</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0719578658382705</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0719578658382705</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>1388.562621856</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>4.169377309511296</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>1476.9891653923698</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>1388.562621856</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1477.6523333137745</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$168,A26,'Species'!$U$2:$U$168))</x:f>
-        <x:v>2051812.7981378108</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>4.169377309511296</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>1476.9891653923698</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>2050891.9479501343</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>920.8501876764931</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0004489998552077</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.00044899985520781944</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0708e4cd074b57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79f62ee2d25f4365"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14182,7 +12768,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -14281,7 +12867,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>74633904.02001323</x:v>
+        <x:v>52178784.33944455</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14295,7 +12881,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>74633904.02001323</x:v>
+        <x:v>57465097.24281223</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14309,7 +12895,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-22455119.68056868</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14323,7 +12909,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-17168806.777200997</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14334,9 +12920,9 @@
         <x:v>EEZ_788</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -14348,47 +12934,19 @@
         <x:v>EEZ_788</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_788</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_788</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8b76d9844c34752"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2887d2a5b12b4ade"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14435,7 +12993,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
